--- a/base_ativa_clientes.xlsx
+++ b/base_ativa_clientes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://algarnet-my.sharepoint.com/personal/pedroofs_algartech_com/Documents/Área de Trabalho/Dashboards/1 - Churn/Painel_Churn_Local (1)/Painel_Churn_Local/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://algarnet-my.sharepoint.com/personal/pedroofs_algartech_com/Documents/Área de Trabalho/Dashboards/1 - Churn/churn_brazil/churn_brazil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{254072AB-E4D9-43E8-A972-964E234CCD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B82A289B-F944-4CDF-AFC2-B2F8997538D4}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{254072AB-E4D9-43E8-A972-964E234CCD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE12DD05-91FE-4BF9-B3DB-61DFB2BBBE61}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="6">
   <si>
     <t>Data</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1013,6 +1013,39 @@
         <v>28044</v>
       </c>
     </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2">
+        <v>48736</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="2">
+        <v>24034</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="2">
+        <v>28044</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
